--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>132014637</v>
       </c>
       <c r="B4" t="n">
-        <v>80351</v>
+        <v>80513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10398-2026 artfynd.xlsx
+++ b/artfynd/A 10398-2026 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>132014637</v>
       </c>
       <c r="B4" t="n">
-        <v>80513</v>
+        <v>80517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
